--- a/data.xlsx
+++ b/data.xlsx
@@ -2457,8 +2457,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:table xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DadosCompset" displayName="DadosCompset" ref="A1:AH320">
-  <ns0:tableColumns count="34">
+<ns0:table xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DadosCompset" displayName="DadosCompset" ref="A1:AI320">
+  <ns0:tableColumns count="35">
     <ns0:tableColumn id="1" name="Empreendimento"/>
     <ns0:tableColumn id="2" name="Fração"/>
     <ns0:tableColumn id="3" name="Piso"/>
@@ -2493,6 +2493,7 @@
     <ns0:tableColumn id="32" name="Justificação Técnica"/>
     <ns0:tableColumn id="33" name="Segmento Análise"/>
     <ns0:tableColumn id="34" name="Disponibilidade Análise"/>
+    <ns0:tableColumn id="35" name="Classe vista comparável"/>
   </ns0:tableColumns>
   <ns0:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </ns0:table>
@@ -2781,6 +2782,7 @@
     <ns0:col min="32" max="32" width="58" customWidth="1"/>
     <ns0:col min="33" max="33" width="19" customWidth="1"/>
     <ns0:col min="34" max="34" width="24" customWidth="1"/>
+    <ns0:col min="35" max="35" width="25" customWidth="1"/>
   </ns0:cols>
   <ns0:sheetData>
     <ns0:row r="1" ht="28.799999237060547">
@@ -2896,6 +2898,11 @@
       <ns0:c r="AH1" s="70" t="inlineStr">
         <ns0:is>
           <ns0:t>Disponibilidade Análise</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AI1" s="70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Classe vista comparável</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -26164,6 +26171,9 @@
       <ns0:c r="AB307" s="74" t="str">
         <ns0:v>Média</ns0:v>
       </ns0:c>
+      <ns0:c r="AI307" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="308">
       <ns0:c r="A308" s="71" t="str">
@@ -26246,6 +26256,9 @@
       <ns0:c r="AB308" s="74" t="str">
         <ns0:v>Média</ns0:v>
       </ns0:c>
+      <ns0:c r="AI308" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="309">
       <ns0:c r="A309" s="71" t="str">
@@ -26328,6 +26341,9 @@
       <ns0:c r="AB309" s="74" t="str">
         <ns0:v>Média</ns0:v>
       </ns0:c>
+      <ns0:c r="AI309" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="310">
       <ns0:c r="A310" s="71" t="str">
@@ -26410,6 +26426,9 @@
       <ns0:c r="AB310" s="74" t="str">
         <ns0:v>Média</ns0:v>
       </ns0:c>
+      <ns0:c r="AI310" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="311">
       <ns0:c r="A311" s="71" t="str">
@@ -26492,6 +26511,9 @@
       <ns0:c r="AB311" s="74" t="str">
         <ns0:v>Média</ns0:v>
       </ns0:c>
+      <ns0:c r="AI311" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="312">
       <ns0:c r="A312" s="71" t="str">
@@ -26574,6 +26596,9 @@
       <ns0:c r="AB312" s="74" t="str">
         <ns0:v>Média</ns0:v>
       </ns0:c>
+      <ns0:c r="AI312" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="313">
       <ns0:c r="A313" s="71" t="str">
@@ -26656,6 +26681,9 @@
       <ns0:c r="AB313" s="74" t="str">
         <ns0:v>Média</ns0:v>
       </ns0:c>
+      <ns0:c r="AI313" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="314">
       <ns0:c r="A314" s="71" t="str">
@@ -26737,6 +26765,9 @@
       </ns0:c>
       <ns0:c r="AB314" s="74" t="str">
         <ns0:v>Média</ns0:v>
+      </ns0:c>
+      <ns0:c r="AI314" t="n">
+        <ns0:v>4</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="315">

--- a/data.xlsx
+++ b/data.xlsx
@@ -11294,7 +11294,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S108" s="74"/>
-      <ns0:c r="T108" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T108" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 29</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U108" s="74"/>
       <ns0:c r="V108" s="74"/>
       <ns0:c r="W108" s="76">
@@ -11393,7 +11397,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S109" s="74"/>
-      <ns0:c r="T109" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T109" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 28</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U109" s="74"/>
       <ns0:c r="V109" s="74"/>
       <ns0:c r="W109" s="76">
@@ -11492,7 +11500,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S110" s="74"/>
-      <ns0:c r="T110" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T110" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sem estacionamento</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U110" s="74"/>
       <ns0:c r="V110" s="74"/>
       <ns0:c r="W110" s="76">
@@ -11591,7 +11603,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S111" s="74"/>
-      <ns0:c r="T111" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T111" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 01</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U111" s="74"/>
       <ns0:c r="V111" s="74"/>
       <ns0:c r="W111" s="76">
@@ -11690,7 +11706,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S112" s="74"/>
-      <ns0:c r="T112" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T112" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 12</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U112" s="74"/>
       <ns0:c r="V112" s="74"/>
       <ns0:c r="W112" s="76">
@@ -11789,7 +11809,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S113" s="74"/>
-      <ns0:c r="T113" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T113" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 22</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U113" s="74"/>
       <ns0:c r="V113" s="74"/>
       <ns0:c r="W113" s="76">
@@ -11888,7 +11912,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S114" s="74"/>
-      <ns0:c r="T114" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T114" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 21</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U114" s="74"/>
       <ns0:c r="V114" s="74"/>
       <ns0:c r="W114" s="76">
@@ -11987,7 +12015,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S115" s="74"/>
-      <ns0:c r="T115" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T115" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sem estacionamento</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U115" s="74"/>
       <ns0:c r="V115" s="74"/>
       <ns0:c r="W115" s="76">
@@ -12086,7 +12118,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S116" s="74"/>
-      <ns0:c r="T116" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T116" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 26</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U116" s="74"/>
       <ns0:c r="V116" s="74"/>
       <ns0:c r="W116" s="76">
@@ -12185,7 +12221,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S117" s="74"/>
-      <ns0:c r="T117" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T117" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 27</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U117" s="74"/>
       <ns0:c r="V117" s="74"/>
       <ns0:c r="W117" s="76">
@@ -12284,7 +12324,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S118" s="74"/>
-      <ns0:c r="T118" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T118" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 02</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U118" s="74"/>
       <ns0:c r="V118" s="74"/>
       <ns0:c r="W118" s="76">
@@ -12383,7 +12427,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S119" s="74"/>
-      <ns0:c r="T119" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T119" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 03</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U119" s="74"/>
       <ns0:c r="V119" s="74"/>
       <ns0:c r="W119" s="76">
@@ -12482,7 +12530,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S120" s="74"/>
-      <ns0:c r="T120" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T120" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 14</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U120" s="74"/>
       <ns0:c r="V120" s="74"/>
       <ns0:c r="W120" s="76">
@@ -12581,7 +12633,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S121" s="74"/>
-      <ns0:c r="T121" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T121" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 20</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U121" s="74"/>
       <ns0:c r="V121" s="74"/>
       <ns0:c r="W121" s="76">
@@ -12680,7 +12736,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S122" s="74"/>
-      <ns0:c r="T122" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T122" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 19</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U122" s="74"/>
       <ns0:c r="V122" s="74"/>
       <ns0:c r="W122" s="76">
@@ -12779,7 +12839,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S123" s="74"/>
-      <ns0:c r="T123" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T123" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 23</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U123" s="74"/>
       <ns0:c r="V123" s="74"/>
       <ns0:c r="W123" s="76">
@@ -12878,7 +12942,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S124" s="74"/>
-      <ns0:c r="T124" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T124" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 24</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U124" s="74"/>
       <ns0:c r="V124" s="74"/>
       <ns0:c r="W124" s="76">
@@ -12977,7 +13045,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S125" s="74"/>
-      <ns0:c r="T125" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T125" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 05</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U125" s="74"/>
       <ns0:c r="V125" s="74"/>
       <ns0:c r="W125" s="76">
@@ -13076,7 +13148,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S126" s="74"/>
-      <ns0:c r="T126" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T126" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sem estacionamento</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U126" s="74"/>
       <ns0:c r="V126" s="74"/>
       <ns0:c r="W126" s="76">
@@ -13175,7 +13251,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S127" s="74"/>
-      <ns0:c r="T127" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T127" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 15</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U127" s="74"/>
       <ns0:c r="V127" s="74"/>
       <ns0:c r="W127" s="76">
@@ -13274,7 +13354,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S128" s="74"/>
-      <ns0:c r="T128" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T128" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 18</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U128" s="74"/>
       <ns0:c r="V128" s="74"/>
       <ns0:c r="W128" s="76">
@@ -13373,7 +13457,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S129" s="74"/>
-      <ns0:c r="T129" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T129" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 37</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U129" s="74"/>
       <ns0:c r="V129" s="74"/>
       <ns0:c r="W129" s="76">
@@ -13472,7 +13560,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S130" s="74"/>
-      <ns0:c r="T130" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T130" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 25</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U130" s="74"/>
       <ns0:c r="V130" s="74"/>
       <ns0:c r="W130" s="76" t="n">
@@ -13571,7 +13663,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S131" s="74"/>
-      <ns0:c r="T131" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T131" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 30</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U131" s="74"/>
       <ns0:c r="V131" s="74"/>
       <ns0:c r="W131" s="76">
@@ -13670,7 +13766,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S132" s="74"/>
-      <ns0:c r="T132" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T132" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 08</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U132" s="74"/>
       <ns0:c r="V132" s="74"/>
       <ns0:c r="W132" s="76">
@@ -13769,7 +13869,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S133" s="74"/>
-      <ns0:c r="T133" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T133" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 17</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U133" s="74"/>
       <ns0:c r="V133" s="74"/>
       <ns0:c r="W133" s="76">
@@ -13868,7 +13972,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S134" s="74"/>
-      <ns0:c r="T134" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T134" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 13</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U134" s="74"/>
       <ns0:c r="V134" s="74"/>
       <ns0:c r="W134" s="76">
@@ -13967,7 +14075,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S135" s="74"/>
-      <ns0:c r="T135" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T135" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 31</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U135" s="74"/>
       <ns0:c r="V135" s="74"/>
       <ns0:c r="W135" s="76">
@@ -14066,7 +14178,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S136" s="74"/>
-      <ns0:c r="T136" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T136" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 11</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U136" s="74"/>
       <ns0:c r="V136" s="74"/>
       <ns0:c r="W136" s="76">
@@ -14165,7 +14281,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S137" s="74"/>
-      <ns0:c r="T137" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T137" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugares 16+17</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U137" s="74"/>
       <ns0:c r="V137" s="74"/>
       <ns0:c r="W137" s="76">
@@ -14269,7 +14389,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S138" s="74"/>
-      <ns0:c r="T138" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T138" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 33</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U138" s="74"/>
       <ns0:c r="V138" s="74"/>
       <ns0:c r="W138" s="76">
@@ -14373,7 +14497,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S139" s="74"/>
-      <ns0:c r="T139" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T139" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 09</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U139" s="74"/>
       <ns0:c r="V139" s="74"/>
       <ns0:c r="W139" s="76">
@@ -14477,7 +14605,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S140" s="74"/>
-      <ns0:c r="T140" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T140" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 34</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U140" s="74"/>
       <ns0:c r="V140" s="74"/>
       <ns0:c r="W140" s="76">
@@ -14581,7 +14713,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S141" s="74"/>
-      <ns0:c r="T141" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T141" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 32</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U141" s="74"/>
       <ns0:c r="V141" s="74"/>
       <ns0:c r="W141" s="76">
@@ -14685,7 +14821,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S142" s="74"/>
-      <ns0:c r="T142" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T142" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugar 35</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U142" s="74"/>
       <ns0:c r="V142" s="74"/>
       <ns0:c r="W142" s="76">
@@ -14789,7 +14929,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S143" s="74"/>
-      <ns0:c r="T143" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T143" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugares 36+38</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U143" s="74"/>
       <ns0:c r="V143" s="74"/>
       <ns0:c r="W143" s="76">
@@ -14888,7 +15032,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S144" s="74"/>
-      <ns0:c r="T144" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T144" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugares 06+07</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U144" s="74"/>
       <ns0:c r="V144" s="74"/>
       <ns0:c r="W144" s="76">
@@ -14987,7 +15135,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S145" s="74"/>
-      <ns0:c r="T145" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T145" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0Inf — Lugar 10</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U145" s="74"/>
       <ns0:c r="V145" s="74"/>
       <ns0:c r="W145" s="76">
@@ -15086,7 +15238,11 @@
         <ns0:v>32</ns0:v>
       </ns0:c>
       <ns0:c r="S146" s="74"/>
-      <ns0:c r="T146" s="74"/>
+      <ns0:c xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T146" s="74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P-1 — Lugares 39+40</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="U146" s="74"/>
       <ns0:c r="V146" s="74"/>
       <ns0:c r="W146" s="76">

--- a/data.xlsx
+++ b/data.xlsx
@@ -11869,7 +11869,7 @@
       </ns0:c>
       <ns0:c r="AF108" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG108" s="74" t="inlineStr">
@@ -11968,7 +11968,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC109" s="73" t="n">
-        <ns0:v>725000</ns0:v>
+        <ns0:v>785000</ns0:v>
       </ns0:c>
       <ns0:c r="AD109" s="74" t="inlineStr">
         <ns0:is>
@@ -11982,7 +11982,7 @@
       </ns0:c>
       <ns0:c r="AF109" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Correção moderada para reforçar a progressão da coluna T2 Sul/Oeste entre pisos.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Correção moderada para reforçar a progressão da coluna T2 Sul/Oeste entre pisos.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG109" s="74" t="inlineStr">
@@ -12081,7 +12081,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC110" s="73" t="n">
-        <ns0:v>400000</ns0:v>
+        <ns0:v>420000</ns0:v>
       </ns0:c>
       <ns0:c r="AD110" s="74" t="inlineStr">
         <ns0:is>
@@ -12095,7 +12095,7 @@
       </ns0:c>
       <ns0:c r="AF110" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG110" s="74" t="inlineStr">
@@ -12194,7 +12194,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC111" s="73" t="n">
-        <ns0:v>500000</ns0:v>
+        <ns0:v>535000</ns0:v>
       </ns0:c>
       <ns0:c r="AD111" s="74" t="inlineStr">
         <ns0:is>
@@ -12208,7 +12208,7 @@
       </ns0:c>
       <ns0:c r="AF111" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG111" s="74" t="inlineStr">
@@ -12307,7 +12307,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC112" s="73" t="n">
-        <ns0:v>475000</ns0:v>
+        <ns0:v>510000</ns0:v>
       </ns0:c>
       <ns0:c r="AD112" s="74" t="inlineStr">
         <ns0:is>
@@ -12321,7 +12321,7 @@
       </ns0:c>
       <ns0:c r="AF112" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG112" s="74" t="inlineStr">
@@ -12420,7 +12420,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC113" s="73" t="n">
-        <ns0:v>735000</ns0:v>
+        <ns0:v>795000</ns0:v>
       </ns0:c>
       <ns0:c r="AD113" s="74" t="inlineStr">
         <ns0:is>
@@ -12434,7 +12434,7 @@
       </ns0:c>
       <ns0:c r="AF113" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): T2+1 de área ampla; ajuste contido face aos T2 próximos.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): T2+1 de área ampla; ajuste contido face aos T2 próximos.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG113" s="74" t="inlineStr">
@@ -12533,7 +12533,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC114" s="73" t="n">
-        <ns0:v>625000</ns0:v>
+        <ns0:v>675000</ns0:v>
       </ns0:c>
       <ns0:c r="AD114" s="74" t="inlineStr">
         <ns0:is>
@@ -12547,7 +12547,7 @@
       </ns0:c>
       <ns0:c r="AF114" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG114" s="74" t="inlineStr">
@@ -12646,7 +12646,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC115" s="73" t="n">
-        <ns0:v>415000</ns0:v>
+        <ns0:v>425000</ns0:v>
       </ns0:c>
       <ns0:c r="AD115" s="74" t="inlineStr">
         <ns0:is>
@@ -12660,7 +12660,7 @@
       </ns0:c>
       <ns0:c r="AF115" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG115" s="74" t="inlineStr">
@@ -12759,7 +12759,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC116" s="73" t="n">
-        <ns0:v>1000000</ns0:v>
+        <ns0:v>1200000</ns0:v>
       </ns0:c>
       <ns0:c r="AD116" s="74" t="inlineStr">
         <ns0:is>
@@ -12773,7 +12773,7 @@
       </ns0:c>
       <ns0:c r="AF116" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): T3 Sul/Este de grande área e exterior relevante; posicionamento abaixo do Apt. 16 preservado.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): T3 Sul/Este de grande área e exterior relevante; posicionamento abaixo do Apt. 16 preservado.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG116" s="74" t="inlineStr">
@@ -12872,7 +12872,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC117" s="73" t="n">
-        <ns0:v>775000</ns0:v>
+        <ns0:v>830000</ns0:v>
       </ns0:c>
       <ns0:c r="AD117" s="74" t="inlineStr">
         <ns0:is>
@@ -12886,7 +12886,7 @@
       </ns0:c>
       <ns0:c r="AF117" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Progressão moderada da coluna T2 Sul/Oeste face ao Apt. 2.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Progressão moderada da coluna T2 Sul/Oeste face ao Apt. 2.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG117" s="74" t="inlineStr">
@@ -12985,7 +12985,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC118" s="73" t="n">
-        <ns0:v>415000</ns0:v>
+        <ns0:v>440000</ns0:v>
       </ns0:c>
       <ns0:c r="AD118" s="74" t="inlineStr">
         <ns0:is>
@@ -12999,7 +12999,7 @@
       </ns0:c>
       <ns0:c r="AF118" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG118" s="74" t="inlineStr">
@@ -13098,7 +13098,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC119" s="73" t="n">
-        <ns0:v>465000</ns0:v>
+        <ns0:v>515000</ns0:v>
       </ns0:c>
       <ns0:c r="AD119" s="74" t="inlineStr">
         <ns0:is>
@@ -13112,7 +13112,7 @@
       </ns0:c>
       <ns0:c r="AF119" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG119" s="74" t="inlineStr">
@@ -13211,7 +13211,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC120" s="73" t="n">
-        <ns0:v>465000</ns0:v>
+        <ns0:v>500000</ns0:v>
       </ns0:c>
       <ns0:c r="AD120" s="74" t="inlineStr">
         <ns0:is>
@@ -13225,7 +13225,7 @@
       </ns0:c>
       <ns0:c r="AF120" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Recomendação condicionada à validação das áreas/características da fração face ao Apt. 12.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Recomendação condicionada à validação das áreas/características da fração face ao Apt. 12.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG120" s="74" t="inlineStr">
@@ -13324,7 +13324,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC121" s="73" t="n">
-        <ns0:v>685000</ns0:v>
+        <ns0:v>735000</ns0:v>
       </ns0:c>
       <ns0:c r="AD121" s="74" t="inlineStr">
         <ns0:is>
@@ -13338,7 +13338,7 @@
       </ns0:c>
       <ns0:c r="AF121" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG121" s="74" t="inlineStr">
@@ -13437,7 +13437,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC122" s="73" t="n">
-        <ns0:v>650000</ns0:v>
+        <ns0:v>705000</ns0:v>
       </ns0:c>
       <ns0:c r="AD122" s="74" t="inlineStr">
         <ns0:is>
@@ -13451,7 +13451,7 @@
       </ns0:c>
       <ns0:c r="AF122" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG122" s="74" t="inlineStr">
@@ -13550,7 +13550,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC123" s="73" t="n">
-        <ns0:v>1100000</ns0:v>
+        <ns0:v>1300000</ns0:v>
       </ns0:c>
       <ns0:c r="AD123" s="74" t="inlineStr">
         <ns0:is>
@@ -13564,7 +13564,7 @@
       </ns0:c>
       <ns0:c r="AF123" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG123" s="74" t="inlineStr">
@@ -13663,7 +13663,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC124" s="73" t="n">
-        <ns0:v>825000</ns0:v>
+        <ns0:v>880000</ns0:v>
       </ns0:c>
       <ns0:c r="AD124" s="74" t="inlineStr">
         <ns0:is>
@@ -13677,7 +13677,7 @@
       </ns0:c>
       <ns0:c r="AF124" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Reforço da progressão interna da coluna T2 Sul/Oeste entre os pisos 2, 3 e 4.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Reforço da progressão interna da coluna T2 Sul/Oeste entre os pisos 2, 3 e 4.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG124" s="74" t="inlineStr">
@@ -13776,7 +13776,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC125" s="73" t="n">
-        <ns0:v>450000</ns0:v>
+        <ns0:v>465000</ns0:v>
       </ns0:c>
       <ns0:c r="AD125" s="74" t="inlineStr">
         <ns0:is>
@@ -13790,7 +13790,7 @@
       </ns0:c>
       <ns0:c r="AF125" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG125" s="74" t="inlineStr">
@@ -13889,7 +13889,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC126" s="73" t="n">
-        <ns0:v>385000</ns0:v>
+        <ns0:v>395000</ns0:v>
       </ns0:c>
       <ns0:c r="AD126" s="74" t="inlineStr">
         <ns0:is>
@@ -13903,7 +13903,7 @@
       </ns0:c>
       <ns0:c r="AF126" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG126" s="74" t="inlineStr">
@@ -14002,7 +14002,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC127" s="73" t="n">
-        <ns0:v>435000</ns0:v>
+        <ns0:v>440000</ns0:v>
       </ns0:c>
       <ns0:c r="AD127" s="74" t="inlineStr">
         <ns0:is>
@@ -14016,7 +14016,7 @@
       </ns0:c>
       <ns0:c r="AF127" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG127" s="74" t="inlineStr">
@@ -14115,7 +14115,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC128" s="73" t="n">
-        <ns0:v>675000</ns0:v>
+        <ns0:v>745000</ns0:v>
       </ns0:c>
       <ns0:c r="AD128" s="74" t="inlineStr">
         <ns0:is>
@@ -14129,7 +14129,7 @@
       </ns0:c>
       <ns0:c r="AF128" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): T2 Este/Oeste no piso 3; ajuste moderado face aos Apt. 14 e 26.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): T2 Este/Oeste no piso 3; ajuste moderado face aos Apt. 14 e 26.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG128" s="74" t="inlineStr">
@@ -14228,7 +14228,7 @@
         <ns0:f t="shared" si="26"/>
       </ns0:c>
       <ns0:c r="AC129" s="73" t="n">
-        <ns0:v>695000</ns0:v>
+        <ns0:v>775000</ns0:v>
       </ns0:c>
       <ns0:c r="AD129" s="74" t="inlineStr">
         <ns0:is>
@@ -14242,7 +14242,7 @@
       </ns0:c>
       <ns0:c r="AF129" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG129" s="74" t="inlineStr">
@@ -14341,7 +14341,7 @@
         <ns0:f t="shared" ref="AB130:AB161" si="32">IF(A130="The View","",IF(OR(J130&lt;2026,Y130="Baixa"),"Alta",IF(W130&lt;0.55,"Média","Baixa")))</ns0:f>
       </ns0:c>
       <ns0:c r="AC130" s="73" t="n">
-        <ns0:v>1000000</ns0:v>
+        <ns0:v>1075000</ns0:v>
       </ns0:c>
       <ns0:c r="AD130" s="74" t="inlineStr">
         <ns0:is>
@@ -14355,7 +14355,7 @@
       </ns0:c>
       <ns0:c r="AF130" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG130" s="74" t="inlineStr">
@@ -14454,7 +14454,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC131" s="73" t="n">
-        <ns0:v>900000</ns0:v>
+        <ns0:v>940000</ns0:v>
       </ns0:c>
       <ns0:c r="AD131" s="74" t="inlineStr">
         <ns0:is>
@@ -14468,7 +14468,7 @@
       </ns0:c>
       <ns0:c r="AF131" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Piso 4, orientação Sul/Oeste e posição premium; reduz diferença excessiva face ao Apt. 23 mantendo Sul/Este valorizado.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Piso 4, orientação Sul/Oeste e posição premium; reduz diferença excessiva face ao Apt. 23 mantendo Sul/Este valorizado.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG131" s="74" t="inlineStr">
@@ -14567,7 +14567,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC132" s="73" t="n">
-        <ns0:v>475000</ns0:v>
+        <ns0:v>490000</ns0:v>
       </ns0:c>
       <ns0:c r="AD132" s="74" t="inlineStr">
         <ns0:is>
@@ -14581,7 +14581,7 @@
       </ns0:c>
       <ns0:c r="AF132" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG132" s="74" t="inlineStr">
@@ -14680,7 +14680,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC133" s="73" t="n">
-        <ns0:v>725000</ns0:v>
+        <ns0:v>815000</ns0:v>
       </ns0:c>
       <ns0:c r="AD133" s="74" t="inlineStr">
         <ns0:is>
@@ -14694,7 +14694,7 @@
       </ns0:c>
       <ns0:c r="AF133" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG133" s="74" t="inlineStr">
@@ -14793,7 +14793,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC134" s="73" t="n">
-        <ns0:v>475000</ns0:v>
+        <ns0:v>510000</ns0:v>
       </ns0:c>
       <ns0:c r="AD134" s="74" t="inlineStr">
         <ns0:is>
@@ -14807,7 +14807,7 @@
       </ns0:c>
       <ns0:c r="AF134" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG134" s="74" t="inlineStr">
@@ -14906,7 +14906,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC135" s="73" t="n">
-        <ns0:v>525000</ns0:v>
+        <ns0:v>565000</ns0:v>
       </ns0:c>
       <ns0:c r="AD135" s="74" t="inlineStr">
         <ns0:is>
@@ -14920,7 +14920,7 @@
       </ns0:c>
       <ns0:c r="AF135" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG135" s="74" t="inlineStr">
@@ -15019,7 +15019,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC136" s="73" t="n">
-        <ns0:v>525000</ns0:v>
+        <ns0:v>545000</ns0:v>
       </ns0:c>
       <ns0:c r="AD136" s="74" t="inlineStr">
         <ns0:is>
@@ -15033,7 +15033,7 @@
       </ns0:c>
       <ns0:c r="AF136" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG136" s="74" t="inlineStr">
@@ -15132,7 +15132,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC137" s="73" t="n">
-        <ns0:v>1100000</ns0:v>
+        <ns0:v>1175000</ns0:v>
       </ns0:c>
       <ns0:c r="AD137" s="74" t="inlineStr">
         <ns0:is>
@@ -15146,7 +15146,7 @@
       </ns0:c>
       <ns0:c r="AF137" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): T2 Sul/Este do piso 5; referência técnica premium fora de comercialização.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): T2 Sul/Este do piso 5; referência técnica premium fora de comercialização.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG137" s="74" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </ns0:c>
       <ns0:c r="AF138" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço técnico de referência. Fração atualmente fora de comercialização.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço técnico de referência. Fração atualmente fora de comercialização.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG138" s="74" t="inlineStr">
@@ -15368,7 +15368,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC139" s="73" t="n">
-        <ns0:v>500000</ns0:v>
+        <ns0:v>515000</ns0:v>
       </ns0:c>
       <ns0:c r="AD139" s="74" t="inlineStr">
         <ns0:is>
@@ -15382,7 +15382,7 @@
       </ns0:c>
       <ns0:c r="AF139" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): T1 do piso 5; referência técnica fora de comercialização.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): T1 do piso 5; referência técnica fora de comercialização.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG139" s="74" t="inlineStr">
@@ -15486,7 +15486,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC140" s="73" t="n">
-        <ns0:v>750000</ns0:v>
+        <ns0:v>795000</ns0:v>
       </ns0:c>
       <ns0:c r="AD140" s="74" t="inlineStr">
         <ns0:is>
@@ -15500,7 +15500,7 @@
       </ns0:c>
       <ns0:c r="AF140" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): T2 Este/Oeste do piso 5; preço técnico para leitura da coluna, fora de comercialização.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): T2 Este/Oeste do piso 5; preço técnico para leitura da coluna, fora de comercialização.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG140" s="74" t="inlineStr">
@@ -15604,7 +15604,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC141" s="73" t="n">
-        <ns0:v>880000</ns0:v>
+        <ns0:v>935000</ns0:v>
       </ns0:c>
       <ns0:c r="AD141" s="74" t="inlineStr">
         <ns0:is>
@@ -15618,7 +15618,7 @@
       </ns0:c>
       <ns0:c r="AF141" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): T2 de área ampla no piso 5; referência técnica fora de comercialização.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): T2 de área ampla no piso 5; referência técnica fora de comercialização.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG141" s="74" t="inlineStr">
@@ -15722,7 +15722,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC142" s="73" t="n">
-        <ns0:v>700000</ns0:v>
+        <ns0:v>800000</ns0:v>
       </ns0:c>
       <ns0:c r="AD142" s="74" t="inlineStr">
         <ns0:is>
@@ -15736,7 +15736,7 @@
       </ns0:c>
       <ns0:c r="AF142" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Duplex singular no piso 5; referência técnica fora de comercialização.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Duplex singular no piso 5; referência técnica fora de comercialização.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG142" s="74" t="inlineStr">
@@ -15840,7 +15840,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC143" s="73" t="n">
-        <ns0:v>1500000</ns0:v>
+        <ns0:v>1750000</ns0:v>
       </ns0:c>
       <ns0:c r="AD143" s="74" t="inlineStr">
         <ns0:is>
@@ -15854,7 +15854,7 @@
       </ns0:c>
       <ns0:c r="AF143" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço elevado mas suportado pelo posicionamento premium, piso 6, orientação Sul/Este e benchmark waterfront.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço elevado mas suportado pelo posicionamento premium, piso 6, orientação Sul/Este e benchmark waterfront.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG143" s="74" t="inlineStr">
@@ -15953,7 +15953,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC144" s="73" t="n">
-        <ns0:v>1105000</ns0:v>
+        <ns0:v>1150000</ns0:v>
       </ns0:c>
       <ns0:c r="AD144" s="74" t="inlineStr">
         <ns0:is>
@@ -15967,7 +15967,7 @@
       </ns0:c>
       <ns0:c r="AF144" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG144" s="74" t="inlineStr">
@@ -16066,7 +16066,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC145" s="73" t="n">
-        <ns0:v>490000</ns0:v>
+        <ns0:v>545000</ns0:v>
       </ns0:c>
       <ns0:c r="AD145" s="74" t="inlineStr">
         <ns0:is>
@@ -16080,7 +16080,7 @@
       </ns0:c>
       <ns0:c r="AF145" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): Preço base tecnicamente alinhado com a concorrência interna e o posicionamento da fração.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG145" s="74" t="inlineStr">
@@ -16179,7 +16179,7 @@
         <ns0:f t="shared" si="32"/>
       </ns0:c>
       <ns0:c r="AC146" s="73" t="n">
-        <ns0:v>1150000</ns0:v>
+        <ns0:v>1300000</ns0:v>
       </ns0:c>
       <ns0:c r="AD146" s="74" t="inlineStr">
         <ns0:is>
@@ -16193,7 +16193,7 @@
       </ns0:c>
       <ns0:c r="AF146" s="74" t="inlineStr">
         <ns0:is>
-          <ns0:t>Preço recomendado definido pela gestão em outubro de 2026. Não resulta de cálculo automático do compset. Enquadramento anterior (setembro de 2026): T3 no último piso com exterior excecional; mantém prémio sobre o T2 Apt. 37 apesar da orientação inferior.</ns0:t>
+          <ns0:t>Preço recomendado da análise independente de outubro de 2026, conforme tabela técnica validada. Não substitui o preço comercial atual. Enquadramento anterior (setembro de 2026): T3 no último piso com exterior excecional; mantém prémio sobre o T2 Apt. 37 apesar da orientação inferior.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AG146" s="74" t="inlineStr">
@@ -62522,11 +62522,11 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="B24" s="95" t="n">
-        <ns0:v>27395000</ns0:v>
+        <ns0:v>29675000</ns0:v>
       </ns0:c>
       <ns0:c r="C24" s="94" t="inlineStr">
         <ns0:is>
-          <ns0:t>Gestão · outubro 2026; não altera PVP ou valores comerciais.</ns0:t>
+          <ns0:t>Análise independente · outubro 2026; não altera PVP ou preços comerciais atuais.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D24" s="94"/>
